--- a/docs/03_tests/部署登録BBテスト.xlsx
+++ b/docs/03_tests/部署登録BBテスト.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\登録\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F035BC2-4B02-4219-9E0B-42BEE2AFAE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE7E5E1-ED0D-41DD-AFF4-0FC85D59B451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{03692441-9742-4EB3-8EDF-D516536FC40E}"/>
   </bookViews>
@@ -360,16 +360,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>20字以上は入力できず</t>
-    <rPh sb="2" eb="5">
-      <t>ジイジョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1-2</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -385,6 +375,10 @@
     <rPh sb="0" eb="3">
       <t>イジョウケイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(2026/05/27にテスト)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -431,7 +425,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -439,9 +433,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1312,6 +1303,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>34636</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>44984</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>34637</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4AC2F9-D985-CA8E-686E-45497D6EE6EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1350818" y="2078182"/>
+          <a:ext cx="2642711" cy="958273"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1632,52 +1667,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4883D4B6-2E5B-46A8-8004-B3FD07F9BA7D}">
-  <dimension ref="A2:G5"/>
+  <dimension ref="A2:B5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="2">
         <v>46167</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1687,7 +1714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F08F508-9B37-42F1-8AFF-F1D607BA643C}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10.4140625" bestFit="1" customWidth="1"/>
@@ -1695,7 +1722,7 @@
     <col min="3" max="3" width="14.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1703,7 +1730,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1717,7 +1744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -1729,7 +1756,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
@@ -1743,7 +1770,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>42</v>
       </c>
@@ -1756,8 +1783,11 @@
       <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
@@ -1771,7 +1801,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
@@ -1871,7 +1901,7 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -1904,31 +1934,28 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE37DE74-1212-4245-B839-7F1BE1BEB625}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="1" t="s">
         <v>45</v>
       </c>

--- a/docs/03_tests/部署登録BBテスト.xlsx
+++ b/docs/03_tests/部署登録BBテスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\登録\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE7E5E1-ED0D-41DD-AFF4-0FC85D59B451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB13CEB-E743-4548-B59A-E99E433400A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{03692441-9742-4EB3-8EDF-D516536FC40E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{03692441-9742-4EB3-8EDF-D516536FC40E}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト仕様" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>テスト番号</t>
     <rPh sb="3" eb="5">
@@ -379,6 +379,39 @@
   </si>
   <si>
     <t>(2026/05/27にテスト)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-3.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リロードをしたとき、Enterページに戻る</t>
+    <rPh sb="19" eb="20">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2-3.リロードをする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値を保持したままConfirmページ</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2-3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-3</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -768,16 +801,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>587375</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>391101</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>78798</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>568964</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>197291</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>372690</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>35655</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -800,8 +833,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="587375" y="4124325"/>
-          <a:ext cx="4582164" cy="3162741"/>
+          <a:off x="9604374" y="4235162"/>
+          <a:ext cx="4588225" cy="3189584"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1054,6 +1087,318 @@
         <a:xfrm>
           <a:off x="14089784" y="707449"/>
           <a:ext cx="2825903" cy="1603951"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>242455</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57727</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>34636</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="矢印: 下 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AA94C1D-7CE8-F90E-5439-4B3689EA305F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6823364" y="4214091"/>
+          <a:ext cx="450272" cy="865909"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>531092</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>286443</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FACA500A-EB25-7F6C-0A10-AEF8D8D5A877}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5137728" y="5437910"/>
+          <a:ext cx="4361988" cy="2089726"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>392548</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>30841</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{317619F1-EC8B-AB2A-4F59-33AC73053FC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4999184" y="8901546"/>
+          <a:ext cx="4244930" cy="1385454"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>288636</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>161637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>80817</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>103910</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="矢印: 下 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFD9B86E-63CF-4500-9FE7-E4D1F0913F45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6869545" y="7781637"/>
+          <a:ext cx="450272" cy="865909"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>62357</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>181741</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>284464</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>57287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="矢印: 下 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F28AD2D-BA96-4A04-8DD9-9D25B1CABF20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="18827411">
+          <a:off x="13166547" y="1659460"/>
+          <a:ext cx="337364" cy="1538289"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>496455</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>23091</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>506610</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1789D797-FD42-259E-70A3-BD1A340CD7E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14316364" y="3024909"/>
+          <a:ext cx="3958701" cy="1720273"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1821,7 +2166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{072D142B-67D6-41D3-89CB-566D1BE07505}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1851,6 +2196,14 @@
       </c>
       <c r="D4" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1861,7 +2214,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21116A7F-D9A7-4F51-8FAF-A83DB76324C5}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -1883,6 +2236,14 @@
       </c>
       <c r="B3" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1893,7 +2254,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F12010-6AC2-4A08-9C26-AC4E8AADD6A7}">
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="16384" width="8.6640625" style="1"/>
@@ -1923,6 +2284,16 @@
     <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="H12" s="1" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="V14" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H24" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
